--- a/fila.xlsx
+++ b/fila.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\batcaverna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A414981-2953-461D-B6FB-5BEAB0F8D1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DF2197-BEE3-4075-9841-4430E8684C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
   <si>
     <t>Bruno Vicente Alves de Lima</t>
   </si>
@@ -453,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -461,10 +461,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -486,7 +482,6 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -520,6 +515,10 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -739,7 +738,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K999"/>
+  <dimension ref="A1:J999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
@@ -749,701 +748,700 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="32" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="29">
+        <v>4</v>
+      </c>
+      <c r="H2" s="29">
+        <v>4</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="16">
+        <v>3</v>
+      </c>
+      <c r="D3" s="16">
+        <v>3</v>
+      </c>
+      <c r="E3" s="16">
+        <v>3</v>
+      </c>
+      <c r="F3" s="16">
+        <v>3</v>
+      </c>
+      <c r="G3" s="16">
+        <v>3</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="16">
+        <v>3</v>
+      </c>
+      <c r="E4" s="16">
+        <v>3</v>
+      </c>
+      <c r="F4" s="16">
+        <v>3</v>
+      </c>
+      <c r="G4" s="16">
+        <v>3</v>
+      </c>
+      <c r="H4" s="16">
+        <v>3</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="30">
+        <v>1</v>
+      </c>
+      <c r="C5" s="30">
+        <v>1</v>
+      </c>
+      <c r="D5" s="30">
+        <v>1</v>
+      </c>
+      <c r="E5" s="30">
+        <v>1</v>
+      </c>
+      <c r="F5" s="30">
+        <v>1</v>
+      </c>
+      <c r="G5" s="30">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8"/>
+      <c r="I5" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="16">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>3</v>
+      </c>
+      <c r="G6" s="16">
+        <v>3</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="30">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8"/>
+      <c r="I7" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="30">
+        <v>1</v>
+      </c>
+      <c r="H8" s="16">
+        <v>3</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="30">
+        <v>1</v>
+      </c>
+      <c r="G9" s="30">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J9" s="2"/>
+    </row>
+    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="30">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="H11" s="8"/>
+      <c r="I11" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="16">
+        <v>3</v>
+      </c>
+      <c r="E12" s="16">
+        <v>3</v>
+      </c>
+      <c r="F12" s="16">
+        <v>3</v>
+      </c>
+      <c r="G12" s="34">
+        <v>2</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="30">
+        <v>1</v>
+      </c>
+      <c r="C13" s="30">
+        <v>1</v>
+      </c>
+      <c r="D13" s="30">
+        <v>1</v>
+      </c>
+      <c r="E13" s="30">
+        <v>1</v>
+      </c>
+      <c r="F13" s="30">
+        <v>1</v>
+      </c>
+      <c r="G13" s="30">
+        <v>1</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9">
+        <v>45689</v>
+      </c>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="30">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="9">
+        <v>45658</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="30">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="30">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="9">
+        <v>45658</v>
+      </c>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="30">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="9">
+        <v>45658</v>
+      </c>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="16">
+        <v>3</v>
+      </c>
+      <c r="D17" s="34">
+        <v>2</v>
+      </c>
+      <c r="E17" s="16">
+        <v>3</v>
+      </c>
+      <c r="F17" s="34">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="9">
+        <v>45658</v>
+      </c>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="16">
+        <v>3</v>
+      </c>
+      <c r="F18" s="34">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9">
+        <v>45658</v>
+      </c>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="30">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="9">
+        <v>45323</v>
+      </c>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="30">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="9">
+        <v>45323</v>
+      </c>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="34">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="9">
+        <v>45292</v>
+      </c>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="30">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="9">
+        <v>45292</v>
+      </c>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="30">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="30">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="9">
+        <v>45292</v>
+      </c>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="16">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="9">
+        <v>44958</v>
+      </c>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="16">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="9">
+        <v>44927</v>
+      </c>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="16">
+        <v>3</v>
+      </c>
+      <c r="I29" s="33" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="30">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" s="35" t="s">
+      <c r="I30" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="J4" s="2"/>
-    </row>
-    <row r="5" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="30">
+        <v>1</v>
+      </c>
+      <c r="I32" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A33" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="30">
+        <v>1</v>
+      </c>
+      <c r="I33" s="7">
+        <v>44593</v>
+      </c>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A34" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="29">
+        <v>4</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="2"/>
+    </row>
+    <row r="35" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="16">
         <v>3</v>
       </c>
-      <c r="B5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="10"/>
-      <c r="I5" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J5" s="2"/>
-    </row>
-    <row r="6" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="10"/>
-      <c r="I6" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J7" s="2"/>
-    </row>
-    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J9" s="2"/>
-    </row>
-    <row r="10" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11">
-        <v>45689</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="H13" s="10"/>
-      <c r="I13" s="11">
-        <v>45689</v>
-      </c>
-      <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11">
-        <v>45658</v>
-      </c>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11">
-        <v>45658</v>
-      </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="11">
-        <v>45658</v>
-      </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="11">
-        <v>45658</v>
-      </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="11">
-        <v>45658</v>
-      </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="11">
-        <v>45323</v>
-      </c>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="11">
-        <v>45323</v>
-      </c>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="11">
-        <v>45292</v>
-      </c>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="11">
-        <v>45292</v>
-      </c>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="11">
-        <v>45292</v>
-      </c>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="11">
-        <v>44958</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="18"/>
-    </row>
-    <row r="25" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="11">
-        <v>44927</v>
-      </c>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A27" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I29" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" s="9">
-        <v>44593</v>
-      </c>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="I34" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="2"/>
-    </row>
-    <row r="35" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="35" t="s">
+      <c r="I35" s="32" t="s">
         <v>44</v>
       </c>
       <c r="J35" s="2"/>
@@ -1457,48 +1455,56 @@
       <c r="I37" s="1"/>
     </row>
     <row r="38" spans="1:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H38" s="6" t="s">
+      <c r="H38" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="I38" s="5"/>
+      <c r="I38" s="36"/>
     </row>
     <row r="39" spans="1:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="H39" s="23"/>
-      <c r="I39" s="24"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="21"/>
     </row>
     <row r="40" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H40" s="25"/>
-      <c r="I40" s="26" t="s">
+      <c r="H40" s="22">
+        <v>1</v>
+      </c>
+      <c r="I40" s="23" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H41" s="27"/>
-      <c r="I41" s="26"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="23"/>
     </row>
     <row r="42" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H42" s="28"/>
-      <c r="I42" s="26" t="s">
+      <c r="H42" s="25">
+        <v>2</v>
+      </c>
+      <c r="I42" s="23" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H43" s="27"/>
-      <c r="I43" s="26"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="23"/>
     </row>
     <row r="44" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H44" s="29"/>
-      <c r="I44" s="30" t="s">
+      <c r="H44" s="26">
+        <v>3</v>
+      </c>
+      <c r="I44" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="H45" s="20"/>
-      <c r="I45" s="22"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="19"/>
     </row>
     <row r="46" spans="1:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H46" s="21"/>
-      <c r="I46" s="31" t="s">
+      <c r="H46" s="18">
+        <v>4</v>
+      </c>
+      <c r="I46" s="28" t="s">
         <v>47</v>
       </c>
     </row>

--- a/fila.xlsx
+++ b/fila.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\batcaverna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2DF2197-BEE3-4075-9841-4430E8684C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8528356-34D3-4AB9-B9FA-9922A526BE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>Bruno Vicente Alves de Lima</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>ÚLTIMA VEZ</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>Três Noites</t>
@@ -902,8 +899,8 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="30" t="s">
-        <v>46</v>
+      <c r="D7" s="30">
+        <v>1</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -983,8 +980,8 @@
       <c r="F11" s="30">
         <v>1</v>
       </c>
-      <c r="G11" s="16" t="s">
-        <v>46</v>
+      <c r="G11" s="16">
+        <v>3</v>
       </c>
       <c r="H11" s="8"/>
       <c r="I11" s="9">
@@ -1505,7 +1502,7 @@
         <v>4</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
